--- a/engine/phar_study/EIPICO_Valuation_Model_09092026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_09092026.xlsx
@@ -2780,19 +2780,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>45.68528385393408</v>
+        <v>45.58896549405187</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>37.81150099018128</v>
+        <v>37.7262922544959</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>31.37379902733586</v>
+        <v>31.29765587745298</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>26.01416352323024</v>
+        <v>25.94555207136375</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>21.4844134990437</v>
+        <v>21.42215348171165</v>
       </c>
     </row>
     <row r="7">
@@ -2824,19 +2824,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>22.8494533223467</v>
+        <v>22.78463350420749</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>24.47046167069734</v>
+        <v>24.40348858286179</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>26.3649795393194</v>
+        <v>26.29548986486675</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>28.621995629933</v>
+        <v>28.54950784362176</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>31.37379902733586</v>
+        <v>31.29765587745298</v>
       </c>
     </row>
     <row r="10">
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>42.16724285094727</v>
+        <v>42.07570398125152</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>36.76279124931227</v>
+        <v>36.6789703231549</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>31.37379902733586</v>
+        <v>31.29765587745298</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>27.93707835693304</v>
+        <v>27.86582035639718</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>22.62112480563719</v>
+        <v>22.55740257890939</v>
       </c>
     </row>
     <row r="13">
@@ -2912,19 +2912,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>49.26491319840814</v>
+        <v>49.16634855819494</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>42.7590534998364</v>
+        <v>42.66864212883422</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>31.37379902733586</v>
+        <v>31.29765587745298</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>23.24147440412117</v>
+        <v>23.17552284075208</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>13.4826848562636</v>
+        <v>13.42896319671105</v>
       </c>
     </row>
     <row r="16">
@@ -2956,19 +2956,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>44.63956596764732</v>
+        <v>44.54806134371371</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>38.00668249749155</v>
+        <v>37.92285861058331</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>31.37379902733586</v>
+        <v>31.29765587745298</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>24.74091555718003</v>
+        <v>24.67245314432251</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>18.10803208702435</v>
+        <v>18.04725041119219</v>
       </c>
     </row>
     <row r="19">
@@ -3000,19 +3000,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>37.36532565503385</v>
+        <v>37.28240163767205</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>34.4684633681824</v>
+        <v>34.38880292827331</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>31.37379902733586</v>
+        <v>31.29765587745298</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>28.0704744073638</v>
+        <v>27.99811659152133</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>24.54723077671931</v>
+        <v>24.47894120238568</v>
       </c>
     </row>
     <row r="22">
@@ -3044,19 +3044,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>36.77869012904124</v>
+        <v>36.69540300280567</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>33.53006026952217</v>
+        <v>33.45106741568353</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>31.37379902733586</v>
+        <v>31.29765587745298</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>29.02402305899556</v>
+        <v>28.95098475382758</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>26.252358655231</v>
+        <v>26.18298173815464</v>
       </c>
     </row>
     <row r="25">
@@ -3088,19 +3088,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>31.34494284548571</v>
+        <v>31.26791082887742</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>33.89811072289919</v>
+        <v>33.81764494749181</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>36.98163985573206</v>
+        <v>36.89702703798336</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>40.80133138880694</v>
+        <v>40.71158146294734</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>45.68528385393408</v>
+        <v>45.58896549405187</v>
       </c>
     </row>
     <row r="27">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>26.81224996276908</v>
+        <v>26.74174255557459</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>28.8405802906386</v>
+        <v>28.76736186699729</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>31.24838047980015</v>
+        <v>31.17194384962523</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>34.1699621733944</v>
+        <v>34.08962062895908</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>37.81150099018128</v>
+        <v>37.7262922544959</v>
       </c>
     </row>
     <row r="28">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>22.8494533223467</v>
+        <v>22.78463350420749</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>24.47046167069734</v>
+        <v>24.40348858286179</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>26.3649795393194</v>
+        <v>26.29548986486675</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>28.621995629933</v>
+        <v>28.54950784362176</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>31.37379902733586</v>
+        <v>31.29765587745298</v>
       </c>
     </row>
     <row r="29">
@@ -3154,19 +3154,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>19.35781412337375</v>
+        <v>19.29799057839121</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>20.65893665542676</v>
+        <v>20.59739533047663</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>22.15790078568526</v>
+        <v>22.09438048451142</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>23.9142656428088</v>
+        <v>23.84842653745394</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>26.01416352323024</v>
+        <v>25.94555207136375</v>
       </c>
     </row>
     <row r="30">
@@ -3176,19 +3176,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>16.26006785654848</v>
+        <v>16.20466325257436</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>17.3073954172165</v>
+        <v>17.25061650460339</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>18.49776590833174</v>
+        <v>18.4394249854069</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>19.87124732344099</v>
+        <v>19.8111041111034</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>21.4844134990437</v>
+        <v>21.42215348171165</v>
       </c>
     </row>
     <row r="32">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B33" s="19" t="n">
-        <v>9321.885127781243</v>
+        <v>9341.733337199817</v>
       </c>
     </row>
     <row r="34">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.3337598757730512</v>
+        <v>0.3342329986819238</v>
       </c>
     </row>
     <row r="35">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>132.9534532778984</v>
+        <v>133.2365385066273</v>
       </c>
     </row>
     <row r="36">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B36" s="24" t="n">
-        <v>1.329534532778984</v>
+        <v>1.332365385066273</v>
       </c>
     </row>
   </sheetData>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="C50" s="21" t="n">
-        <v>0.2481</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">

--- a/engine/phar_study/EIPICO_Valuation_Model_09092026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_09092026.xlsx
@@ -2780,19 +2780,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>45.58896549405187</v>
+        <v>116.8898630835042</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>37.7262922544959</v>
+        <v>101.2789720165504</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>31.29765587745298</v>
+        <v>88.52006108866607</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>25.94555207136375</v>
+        <v>77.90184598932781</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>21.42215348171165</v>
+        <v>68.93126868579441</v>
       </c>
     </row>
     <row r="7">
@@ -2824,19 +2824,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>22.78463350420749</v>
+        <v>64.67936187349869</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>24.40348858286179</v>
+        <v>69.10988707359989</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>26.29548986486675</v>
+        <v>74.36062734942834</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>28.54950784362176</v>
+        <v>80.69844681104422</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>31.29765587745298</v>
+        <v>88.52006108866607</v>
       </c>
     </row>
     <row r="10">
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>42.07570398125152</v>
+        <v>109.909246760291</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>36.6789703231549</v>
+        <v>99.19778949436856</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>31.29765587745298</v>
+        <v>88.52006108866607</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>27.86582035639718</v>
+        <v>81.71242135425572</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>22.55740257890939</v>
+        <v>71.18563258213437</v>
       </c>
     </row>
     <row r="13">
@@ -2912,19 +2912,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>49.16634855819494</v>
+        <v>108.4848543058153</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>42.66864212883422</v>
+        <v>101.2249294995792</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>31.29765587745298</v>
+        <v>88.52006108866607</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>23.17552284075208</v>
+        <v>79.44515508087099</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>13.42896319671105</v>
+        <v>68.55526787151685</v>
       </c>
     </row>
     <row r="16">
@@ -2956,19 +2956,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>44.54806134371371</v>
+        <v>101.7704665549268</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>37.92285861058331</v>
+        <v>95.14526382179639</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>31.29765587745298</v>
+        <v>88.52006108866607</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>24.67245314432251</v>
+        <v>81.89485835553559</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>18.04725041119219</v>
+        <v>75.26965562240521</v>
       </c>
     </row>
     <row r="19">
@@ -3000,19 +3000,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>37.28240163767205</v>
+        <v>85.52224705897167</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>34.38880292827331</v>
+        <v>86.95665722192979</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>31.29765587745298</v>
+        <v>88.52006108866607</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>27.99811659152133</v>
+        <v>90.22015131507219</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>24.47894120238568</v>
+        <v>92.06491659119241</v>
       </c>
     </row>
     <row r="22">
@@ -3044,19 +3044,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>36.69540300280567</v>
+        <v>94.05805328643289</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>33.45106741568353</v>
+        <v>90.73122059789067</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>31.29765587745298</v>
+        <v>88.52006108866607</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>28.95098475382758</v>
+        <v>86.10739228390462</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>26.18298173815464</v>
+        <v>83.25689216681162</v>
       </c>
     </row>
     <row r="25">
@@ -3088,19 +3088,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>31.26791082887742</v>
+        <v>80.02315964013067</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>33.81764494749181</v>
+        <v>86.47691859854055</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>36.89702703798336</v>
+        <v>94.35069829981471</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>40.71158146294734</v>
+        <v>104.1955229591783</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>45.58896549405187</v>
+        <v>116.8898630835042</v>
       </c>
     </row>
     <row r="27">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>26.74174255557459</v>
+        <v>71.83801766073219</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>28.76736186699729</v>
+        <v>77.16111252125518</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>31.17194384962523</v>
+        <v>83.5556605690013</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>34.08962062895908</v>
+        <v>91.40089781927408</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>37.7262922544959</v>
+        <v>101.2789720165504</v>
       </c>
     </row>
     <row r="28">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>22.78463350420749</v>
+        <v>64.67936187349869</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>24.40348858286179</v>
+        <v>69.10988707359989</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>26.29548986486675</v>
+        <v>74.36062734942834</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>28.54950784362176</v>
+        <v>80.69844681104422</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>31.29765587745298</v>
+        <v>88.52006108866607</v>
       </c>
     </row>
     <row r="29">
@@ -3154,19 +3154,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>19.29799057839121</v>
+        <v>58.36941123562625</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>20.59739533047663</v>
+        <v>62.08627940604708</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>22.09438048451142</v>
+        <v>66.43883146809664</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>23.84842653745394</v>
+        <v>71.61843657281135</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>25.94555207136375</v>
+        <v>77.90184598932781</v>
       </c>
     </row>
     <row r="30">
@@ -3176,19 +3176,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>16.20466325257436</v>
+        <v>52.76904724352868</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>17.25061650460339</v>
+        <v>55.90889564950249</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>18.4394249854069</v>
+        <v>59.54665847378946</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>19.8111041111034</v>
+        <v>63.82180735359283</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>21.42215348171165</v>
+        <v>68.93126868579441</v>
       </c>
     </row>
     <row r="32">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B33" s="19" t="n">
-        <v>9341.733337199817</v>
+        <v>3773.572941928797</v>
       </c>
     </row>
     <row r="34">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.3342329986819238</v>
+        <v>0.1528692408313553</v>
       </c>
     </row>
     <row r="35">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>133.2365385066273</v>
+        <v>53.82061106184076</v>
       </c>
     </row>
     <row r="36">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B36" s="24" t="n">
-        <v>1.332365385066273</v>
+        <v>0.5382061106184076</v>
       </c>
     </row>
   </sheetData>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 79% of core enterprise value, 61% of total</t>
+          <t>Terminal value 79% of core enterprise value, 68% of total</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 79% of core enterprise value, 64% of total</t>
+          <t>Terminal value 79% of core enterprise value, 70% of total</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Justified 1.16 times book</t>
+          <t>Justified 1.98 times book</t>
         </is>
       </c>
     </row>
@@ -4725,19 +4725,19 @@
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="E14" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F14" s="17" t="n">
         <v>0.075</v>
       </c>
-      <c r="F14" s="17" t="n">
-        <v>0.065</v>
-      </c>
       <c r="G14" s="17" t="n">
-        <v>0.055</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>0.4792091017585894</v>
+        <v>0.3622543626257113</v>
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="B36" s="6">
-        <f>1-Assumptions!$C$62/0.18754717</f>
+        <f>1-Assumptions!$C$62/0.27108978</f>
         <v/>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="B25" s="13">
-        <f>-717.450174</f>
+        <f>-755.175131</f>
         <v/>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="B44" s="13">
-        <f>B43+-969.166571</f>
+        <f>B43+-1006.891528</f>
         <v/>
       </c>
     </row>
